--- a/test_file.xlsx
+++ b/test_file.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2e0065511815a88e/Coding/llp_system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59F9F713538C4A17DB2711591598305C7FE2B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4247CF1D-2392-428F-9866-B7336DD17E34}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_2B59F9F713830768077B29115963403567F5E5ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9800A68E-902A-4804-8C2A-CD30FB8EC80D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>id</t>
   </si>
@@ -31,6 +31,9 @@
     <t>ts</t>
   </si>
   <si>
+    <t>p_ts</t>
+  </si>
+  <si>
     <t>art_ph</t>
   </si>
   <si>
@@ -68,6 +71,27 @@
   </si>
   <si>
     <t>k</t>
+  </si>
+  <si>
+    <t>glu</t>
+  </si>
+  <si>
+    <t>lac</t>
+  </si>
+  <si>
+    <t>vo2</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>test_note 26</t>
+  </si>
+  <si>
+    <t>test_note 78</t>
+  </si>
+  <si>
+    <t>test_note 69</t>
   </si>
 </sst>
 </file>
@@ -430,13 +454,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,8 +510,23 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -494,49 +534,64 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1782572042</v>
+        <v>1789237588</v>
       </c>
       <c r="D2">
-        <v>0.46</v>
+        <v>1789237588</v>
       </c>
       <c r="E2">
-        <v>7.64</v>
+        <v>0.05</v>
       </c>
       <c r="F2">
-        <v>0.48</v>
+        <v>1.05</v>
       </c>
       <c r="G2">
-        <v>1.5</v>
+        <v>0.36</v>
       </c>
       <c r="H2">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="I2">
-        <v>7.56</v>
+        <v>1.6</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="K2">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="L2">
-        <v>0.16</v>
+        <v>1.48</v>
       </c>
       <c r="M2">
-        <v>0.39</v>
+        <v>3.5</v>
       </c>
       <c r="N2">
-        <v>0.1</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="O2">
-        <v>0.83</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="P2">
-        <v>0.96</v>
+        <v>1.17</v>
+      </c>
+      <c r="Q2">
+        <v>1.24</v>
+      </c>
+      <c r="R2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S2">
+        <v>0.87</v>
+      </c>
+      <c r="T2">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="U2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -544,49 +599,61 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1782572052</v>
+        <v>1789237594</v>
       </c>
       <c r="D3">
-        <v>0.62</v>
+        <v>1789237594</v>
       </c>
       <c r="E3">
-        <v>0.14000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="F3">
-        <v>1.03</v>
+        <v>46</v>
       </c>
       <c r="G3">
-        <v>1.72</v>
+        <v>0.31</v>
       </c>
       <c r="H3">
-        <v>3.21</v>
+        <v>0.64</v>
       </c>
       <c r="I3">
-        <v>2.44</v>
+        <v>1.4</v>
       </c>
       <c r="J3">
-        <v>0.49</v>
+        <v>0.9</v>
       </c>
       <c r="K3">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="L3">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="M3">
-        <v>0.98</v>
+        <v>0.66</v>
       </c>
       <c r="N3">
-        <v>4.6100000000000003</v>
+        <v>1.06</v>
       </c>
       <c r="O3">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="P3">
-        <v>0.41</v>
+        <v>1.06</v>
+      </c>
+      <c r="Q3">
+        <v>3.14</v>
+      </c>
+      <c r="R3">
+        <v>0.82</v>
+      </c>
+      <c r="S3">
+        <v>0.61</v>
+      </c>
+      <c r="T3">
+        <v>0.48</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -594,49 +661,64 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1782572057</v>
+        <v>1789237600</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>1789237600</v>
       </c>
       <c r="E4">
-        <v>2.2599999999999998</v>
+        <v>0.72</v>
       </c>
       <c r="F4">
-        <v>0.2</v>
+        <v>20.329999999999998</v>
       </c>
       <c r="G4">
-        <v>1.35</v>
+        <v>0.21</v>
       </c>
       <c r="H4">
-        <v>0.32</v>
+        <v>0.96</v>
       </c>
       <c r="I4">
-        <v>0.01</v>
+        <v>1.94</v>
       </c>
       <c r="J4">
-        <v>0.18</v>
+        <v>2.96</v>
       </c>
       <c r="K4">
-        <v>57</v>
+        <v>0.73</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="M4">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="N4">
-        <v>0.1</v>
+        <v>9.4</v>
       </c>
       <c r="O4">
-        <v>2.68</v>
+        <v>0.79</v>
       </c>
       <c r="P4">
-        <v>0.24</v>
+        <v>3.14</v>
+      </c>
+      <c r="Q4">
+        <v>1.56</v>
+      </c>
+      <c r="R4">
+        <v>0.94</v>
+      </c>
+      <c r="S4">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="T4">
+        <v>5.2</v>
+      </c>
+      <c r="U4" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -644,49 +726,61 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1782572061</v>
+        <v>1789237606</v>
       </c>
       <c r="D5">
-        <v>0.9</v>
+        <v>1789237606</v>
       </c>
       <c r="E5">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="F5">
-        <v>0.43</v>
+        <v>1.47</v>
       </c>
       <c r="G5">
-        <v>0.66</v>
+        <v>0.86</v>
       </c>
       <c r="H5">
-        <v>1.43</v>
+        <v>0.25</v>
       </c>
       <c r="I5">
-        <v>5.14</v>
+        <v>0.47</v>
       </c>
       <c r="J5">
-        <v>2.41</v>
+        <v>1.18</v>
       </c>
       <c r="K5">
-        <v>0.05</v>
+        <v>1.01</v>
       </c>
       <c r="L5">
-        <v>0.73</v>
+        <v>2.79</v>
       </c>
       <c r="M5">
-        <v>1.1200000000000001</v>
+        <v>20.25</v>
       </c>
       <c r="N5">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>1.34</v>
+        <v>2.02</v>
       </c>
       <c r="P5">
-        <v>3.08</v>
+        <v>0.34</v>
+      </c>
+      <c r="Q5">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="R5">
+        <v>0.98</v>
+      </c>
+      <c r="S5">
+        <v>1.19</v>
+      </c>
+      <c r="T5">
+        <v>0.46</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -694,49 +788,61 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1783259344</v>
+        <v>1789237612</v>
       </c>
       <c r="D6">
-        <v>0.66</v>
+        <v>1789237612</v>
       </c>
       <c r="E6">
-        <v>2.4500000000000002</v>
+        <v>1.97</v>
       </c>
       <c r="F6">
-        <v>1.38</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="G6">
-        <v>0.45</v>
+        <v>1.58</v>
       </c>
       <c r="H6">
-        <v>0.18</v>
+        <v>0.96</v>
       </c>
       <c r="I6">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
       <c r="J6">
-        <v>3.38</v>
+        <v>0.47</v>
       </c>
       <c r="K6">
-        <v>1.01</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="L6">
-        <v>1.49</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M6">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="N6">
-        <v>7.73</v>
+        <v>1.74</v>
       </c>
       <c r="O6">
-        <v>1.91</v>
+        <v>0.77</v>
       </c>
       <c r="P6">
-        <v>2.16</v>
+        <v>1.4</v>
+      </c>
+      <c r="Q6">
+        <v>0.83</v>
+      </c>
+      <c r="R6">
+        <v>0.63</v>
+      </c>
+      <c r="S6">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="T6">
+        <v>0.06</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -744,49 +850,61 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>1783259352</v>
+        <v>1789237618</v>
       </c>
       <c r="D7">
+        <v>1789237618</v>
+      </c>
+      <c r="E7">
+        <v>0.04</v>
+      </c>
+      <c r="F7">
+        <v>0.78</v>
+      </c>
+      <c r="G7">
+        <v>1.06</v>
+      </c>
+      <c r="H7">
+        <v>0.7</v>
+      </c>
+      <c r="I7">
+        <v>16.5</v>
+      </c>
+      <c r="J7">
+        <v>0.86</v>
+      </c>
+      <c r="K7">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L7">
+        <v>5.17</v>
+      </c>
+      <c r="M7">
         <v>0.89</v>
       </c>
-      <c r="E7">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="F7">
-        <v>1.18</v>
-      </c>
-      <c r="G7">
-        <v>0.33</v>
-      </c>
-      <c r="H7">
-        <v>2.12</v>
-      </c>
-      <c r="I7">
-        <v>1.48</v>
-      </c>
-      <c r="J7">
-        <v>0.18</v>
-      </c>
-      <c r="K7">
-        <v>0.64</v>
-      </c>
-      <c r="L7">
-        <v>0.47</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
       <c r="N7">
-        <v>0.65</v>
+        <v>1.69</v>
       </c>
       <c r="O7">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="P7">
-        <v>3.8</v>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Q7">
+        <v>0.22</v>
+      </c>
+      <c r="R7">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S7">
+        <v>34.5</v>
+      </c>
+      <c r="T7">
+        <v>1.71</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -794,96 +912,75 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>1783259381</v>
+        <v>1789237624</v>
       </c>
       <c r="D8">
-        <v>1.32</v>
+        <v>1789237624</v>
       </c>
       <c r="E8">
-        <v>0.96</v>
+        <v>0.33</v>
       </c>
       <c r="F8">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="G8">
-        <v>1.98</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="H8">
-        <v>0.4</v>
+        <v>2.27</v>
       </c>
       <c r="I8">
-        <v>0.93</v>
+        <v>0.47</v>
       </c>
       <c r="J8">
-        <v>6.38</v>
+        <v>0.83</v>
       </c>
       <c r="K8">
-        <v>5.18</v>
+        <v>0.61</v>
       </c>
       <c r="L8">
-        <v>0.51</v>
+        <v>0.22</v>
       </c>
       <c r="M8">
-        <v>0.68</v>
+        <v>0.98</v>
       </c>
       <c r="N8">
-        <v>0.28000000000000003</v>
+        <v>4.82</v>
       </c>
       <c r="O8">
-        <v>0.19</v>
+        <v>1.71</v>
       </c>
       <c r="P8">
-        <v>0.32</v>
+        <v>0.39</v>
+      </c>
+      <c r="Q8">
+        <v>12.25</v>
+      </c>
+      <c r="R8">
+        <v>0.11</v>
+      </c>
+      <c r="S8">
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="T8">
+        <v>0.37</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>1783259396</v>
+        <v>1789239546</v>
       </c>
       <c r="D9">
-        <v>0.78</v>
-      </c>
-      <c r="E9">
-        <v>0.22</v>
-      </c>
-      <c r="F9">
-        <v>5.56</v>
-      </c>
-      <c r="G9">
-        <v>0.01</v>
-      </c>
-      <c r="H9">
-        <v>2.91</v>
-      </c>
-      <c r="I9">
-        <v>0.98</v>
-      </c>
-      <c r="J9">
-        <v>2.84</v>
-      </c>
-      <c r="K9">
-        <v>4.83</v>
-      </c>
-      <c r="L9">
-        <v>0.68</v>
-      </c>
-      <c r="M9">
-        <v>0.48</v>
-      </c>
-      <c r="N9">
-        <v>4.93</v>
-      </c>
-      <c r="O9">
-        <v>4</v>
-      </c>
-      <c r="P9">
-        <v>2.5</v>
+        <v>1789239546</v>
+      </c>
+      <c r="U9" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/test_file.xlsx
+++ b/test_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2e0065511815a88e/Coding/llp_system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_2B59F9F713830768077B29115963403567F5E5ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9800A68E-902A-4804-8C2A-CD30FB8EC80D}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="6_{EF2EDAA6-2B85-46BC-9108-0C9588396574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA9E40E3-146F-4FD5-A0FB-B4F7E5DF4AC3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>id</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>test_note 69</t>
+  </si>
+  <si>
+    <t>late test not 82</t>
   </si>
 </sst>
 </file>
@@ -454,11 +457,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
@@ -968,19 +971,456 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>1789239546</v>
+        <v>1789237630</v>
       </c>
       <c r="D9">
-        <v>1789239546</v>
+        <v>1789237630</v>
+      </c>
+      <c r="E9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.91</v>
+      </c>
+      <c r="G9">
+        <v>2.65</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9">
+        <v>0.27</v>
+      </c>
+      <c r="J9">
+        <v>0.78</v>
+      </c>
+      <c r="K9">
+        <v>7.64</v>
+      </c>
+      <c r="L9">
+        <v>0.79</v>
+      </c>
+      <c r="M9">
+        <v>1.52</v>
+      </c>
+      <c r="N9">
+        <v>0.01</v>
+      </c>
+      <c r="O9">
+        <v>0.01</v>
+      </c>
+      <c r="P9">
+        <v>1.5</v>
+      </c>
+      <c r="Q9">
+        <v>0.94</v>
+      </c>
+      <c r="R9">
+        <v>0.17</v>
+      </c>
+      <c r="S9">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="T9">
+        <v>10.43</v>
       </c>
       <c r="U9" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1789304708</v>
+      </c>
+      <c r="D10">
+        <v>1789304708</v>
+      </c>
+      <c r="E10">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="F10">
+        <v>1.22</v>
+      </c>
+      <c r="G10">
+        <v>3.75</v>
+      </c>
+      <c r="H10">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I10">
+        <v>0.24</v>
+      </c>
+      <c r="J10">
+        <v>0.72</v>
+      </c>
+      <c r="K10">
+        <v>0.16</v>
+      </c>
+      <c r="L10">
+        <v>0.97</v>
+      </c>
+      <c r="M10">
+        <v>0.02</v>
+      </c>
+      <c r="N10">
+        <v>1.7</v>
+      </c>
+      <c r="O10">
+        <v>0.73</v>
+      </c>
+      <c r="P10">
+        <v>61</v>
+      </c>
+      <c r="Q10">
+        <v>2.74</v>
+      </c>
+      <c r="R10">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S10">
+        <v>1.51</v>
+      </c>
+      <c r="T10">
+        <v>29.67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1789304813</v>
+      </c>
+      <c r="D11">
+        <v>1789304813</v>
+      </c>
+      <c r="E11">
+        <v>33</v>
+      </c>
+      <c r="F11">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="G11">
+        <v>1.76</v>
+      </c>
+      <c r="H11">
+        <v>0.68</v>
+      </c>
+      <c r="I11">
+        <v>0.6</v>
+      </c>
+      <c r="J11">
+        <v>10.71</v>
+      </c>
+      <c r="K11">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L11">
+        <v>4.67</v>
+      </c>
+      <c r="M11">
+        <v>0.88</v>
+      </c>
+      <c r="N11">
+        <v>0.09</v>
+      </c>
+      <c r="O11">
+        <v>1.5</v>
+      </c>
+      <c r="P11">
+        <v>1.54</v>
+      </c>
+      <c r="Q11">
+        <v>5.82</v>
+      </c>
+      <c r="R11">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="S11">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="T11">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1789304975</v>
+      </c>
+      <c r="D12">
+        <v>1789304975</v>
+      </c>
+      <c r="E12">
+        <v>0.25</v>
+      </c>
+      <c r="F12">
+        <v>1.3</v>
+      </c>
+      <c r="G12">
+        <v>0.25</v>
+      </c>
+      <c r="H12">
+        <v>1.43</v>
+      </c>
+      <c r="I12">
+        <v>13.6</v>
+      </c>
+      <c r="J12">
+        <v>0.59</v>
+      </c>
+      <c r="K12">
+        <v>0.92</v>
+      </c>
+      <c r="L12">
+        <v>1.68</v>
+      </c>
+      <c r="M12">
+        <v>0.65</v>
+      </c>
+      <c r="N12">
+        <v>0.82</v>
+      </c>
+      <c r="O12">
+        <v>0.48</v>
+      </c>
+      <c r="P12">
+        <v>1.31</v>
+      </c>
+      <c r="Q12">
+        <v>0.05</v>
+      </c>
+      <c r="R12">
+        <v>0.03</v>
+      </c>
+      <c r="S12">
+        <v>5.4</v>
+      </c>
+      <c r="T12">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1789305069</v>
+      </c>
+      <c r="D13">
+        <v>1789305069</v>
+      </c>
+      <c r="E13">
+        <v>1.25</v>
+      </c>
+      <c r="F13">
+        <v>1.25</v>
+      </c>
+      <c r="G13">
+        <v>0.9</v>
+      </c>
+      <c r="H13">
+        <v>0.7</v>
+      </c>
+      <c r="I13">
+        <v>1.03</v>
+      </c>
+      <c r="J13">
+        <v>15</v>
+      </c>
+      <c r="K13">
+        <v>0.76</v>
+      </c>
+      <c r="L13">
+        <v>3</v>
+      </c>
+      <c r="M13">
+        <v>0.94</v>
+      </c>
+      <c r="N13">
+        <v>0.88</v>
+      </c>
+      <c r="O13">
+        <v>1.24</v>
+      </c>
+      <c r="P13">
+        <v>6.9</v>
+      </c>
+      <c r="Q13">
+        <v>1.76</v>
+      </c>
+      <c r="R13">
+        <v>0.12</v>
+      </c>
+      <c r="S13">
+        <v>0.54</v>
+      </c>
+      <c r="T13">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1789305135</v>
+      </c>
+      <c r="D14">
+        <v>1789305135</v>
+      </c>
+      <c r="E14">
+        <v>0.64</v>
+      </c>
+      <c r="F14">
+        <v>0.66</v>
+      </c>
+      <c r="G14">
+        <v>2.44</v>
+      </c>
+      <c r="H14">
+        <v>0.4</v>
+      </c>
+      <c r="I14">
+        <v>2.39</v>
+      </c>
+      <c r="J14">
+        <v>0.43</v>
+      </c>
+      <c r="K14">
+        <v>2.93</v>
+      </c>
+      <c r="L14">
+        <v>2.68</v>
+      </c>
+      <c r="M14">
+        <v>3.22</v>
+      </c>
+      <c r="N14">
+        <v>2.42</v>
+      </c>
+      <c r="O14">
+        <v>3.33</v>
+      </c>
+      <c r="P14">
+        <v>12</v>
+      </c>
+      <c r="Q14">
+        <v>0.42</v>
+      </c>
+      <c r="R14">
+        <v>0.03</v>
+      </c>
+      <c r="S14">
+        <v>0.51</v>
+      </c>
+      <c r="T14">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1789305210</v>
+      </c>
+      <c r="D15">
+        <v>1789305210</v>
+      </c>
+      <c r="E15">
+        <v>2.72</v>
+      </c>
+      <c r="F15">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="G15">
+        <v>0.34</v>
+      </c>
+      <c r="H15">
+        <v>1.3</v>
+      </c>
+      <c r="I15">
+        <v>1.42</v>
+      </c>
+      <c r="J15">
+        <v>1.52</v>
+      </c>
+      <c r="K15">
+        <v>3</v>
+      </c>
+      <c r="L15">
+        <v>19.8</v>
+      </c>
+      <c r="M15">
+        <v>0.03</v>
+      </c>
+      <c r="N15">
+        <v>3.07</v>
+      </c>
+      <c r="O15">
+        <v>1.27</v>
+      </c>
+      <c r="P15">
+        <v>1.04</v>
+      </c>
+      <c r="Q15">
+        <v>91</v>
+      </c>
+      <c r="R15">
+        <v>10.57</v>
+      </c>
+      <c r="S15">
+        <v>2.39</v>
+      </c>
+      <c r="T15">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1789306090</v>
+      </c>
+      <c r="D16">
+        <v>1789306090</v>
+      </c>
+      <c r="U16" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/test_file.xlsx
+++ b/test_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,6 +1464,356 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1789903281</v>
+      </c>
+      <c r="D17" t="n">
+        <v>161134</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>test note nr: 63</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1789903300</v>
+      </c>
+      <c r="D18" t="n">
+        <v>161153</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>test note nr: 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1789903524</v>
+      </c>
+      <c r="D19" t="n">
+        <v>161377</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>test note nr: 63</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1789903762</v>
+      </c>
+      <c r="D20" t="n">
+        <v>161615</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>test note nr: 81</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1789903836</v>
+      </c>
+      <c r="D21" t="n">
+        <v>161689</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>test note nr: 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1789903980</v>
+      </c>
+      <c r="D22" t="n">
+        <v>161833</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>test note nr: 86</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1789904011</v>
+      </c>
+      <c r="D23" t="n">
+        <v>161864</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>test note nr: 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1789904011</v>
+      </c>
+      <c r="D24" t="n">
+        <v>161864</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>late test not 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1789904017</v>
+      </c>
+      <c r="D25" t="n">
+        <v>161870</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>test note nr: 39</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1789904017</v>
+      </c>
+      <c r="D26" t="n">
+        <v>161870</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>late test not 37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
